--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA90CBE-79F0-412E-AA78-78C34AA33B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A36FD6-E565-4E4F-AE23-4C79F278C1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="172">
   <si>
     <t>CPF</t>
   </si>
@@ -533,13 +533,19 @@
   </si>
   <si>
     <t>ESCOLA ESTADUAL PROFESSORA DIVA GOMES DA SILVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>tolentinoalexandre534@gmail.com</t>
+  </si>
+  <si>
+    <t>E-MAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -548,6 +554,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -567,14 +579,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -887,15 +902,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -908,8 +924,11 @@
       <c r="D1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -920,7 +939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -931,7 +950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>167</v>
       </c>
@@ -942,7 +961,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -953,7 +972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -964,7 +983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -975,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -986,7 +1005,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -997,7 +1016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1008,7 +1027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1019,7 +1038,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1030,7 +1049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1041,7 +1060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1052,7 +1071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1063,7 +1082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1085,7 +1104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1096,7 +1115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1107,7 +1126,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1118,7 +1137,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1129,7 +1148,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1139,8 +1158,11 @@
       <c r="D22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1151,7 +1173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1162,7 +1184,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1173,7 +1195,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1184,7 +1206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1195,7 +1217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1206,7 +1228,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1217,7 +1239,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1228,7 +1250,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1239,7 +1261,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2516,7 +2538,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E22" r:id="rId1" xr:uid="{DF9AA0FA-640D-4BBA-B718-4F7C2131015A}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 2 3 4 - Copia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{8798D671-E798-4ABF-823C-27E61BC2478E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49334AA3-E539-4821-88E0-DB681C7C4832}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5978884F-8FA8-491A-8286-B25C38B0C403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="171">
   <si>
     <t>CPF</t>
   </si>
@@ -524,6 +524,18 @@
   </si>
   <si>
     <t>AYRANA GOMES FERREIRA</t>
+  </si>
+  <si>
+    <t>ROSEANE SOUZA PEREIRA</t>
+  </si>
+  <si>
+    <t>roseanesouza@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ALINE REIS DOS SANTOS MARTINS</t>
+  </si>
+  <si>
+    <t>alinereis@seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -588,10 +600,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -891,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -1381,642 +1389,667 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" t="s">
-        <v>56</v>
+        <v>167</v>
+      </c>
+      <c r="B35">
+        <v>3496300116</v>
+      </c>
+      <c r="D35">
+        <v>3496300116</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>59</v>
       </c>
-      <c r="C38">
+      <c r="C41">
         <v>17021502</v>
       </c>
-      <c r="D38">
+      <c r="D41">
         <v>17021502</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39">
-        <v>17021685</v>
-      </c>
-      <c r="D39">
-        <v>17021685</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40">
-        <v>17021553</v>
-      </c>
-      <c r="D40">
-        <v>17021553</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41">
-        <v>17052351</v>
-      </c>
-      <c r="D41">
-        <v>17052351</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C42">
-        <v>17021243</v>
+        <v>17021685</v>
       </c>
       <c r="D42">
-        <v>17021243</v>
+        <v>17021685</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C43">
-        <v>17023181</v>
+        <v>17021553</v>
       </c>
       <c r="D43">
-        <v>17023181</v>
+        <v>17021553</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C44">
-        <v>17048826</v>
+        <v>17052351</v>
       </c>
       <c r="D44">
-        <v>17048826</v>
+        <v>17052351</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C45">
-        <v>17020336</v>
+        <v>17021243</v>
       </c>
       <c r="D45">
-        <v>17020336</v>
+        <v>17021243</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C46">
-        <v>17018382</v>
+        <v>17023181</v>
       </c>
       <c r="D46">
-        <v>17018382</v>
+        <v>17023181</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C47">
-        <v>17021251</v>
+        <v>17048826</v>
       </c>
       <c r="D47">
-        <v>17021251</v>
+        <v>17048826</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C48">
-        <v>17020590</v>
+        <v>17020336</v>
       </c>
       <c r="D48">
-        <v>17020590</v>
+        <v>17020336</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C49">
-        <v>17052963</v>
+        <v>17018382</v>
       </c>
       <c r="D49">
-        <v>17052963</v>
+        <v>17018382</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C50">
-        <v>17022819</v>
+        <v>17021251</v>
       </c>
       <c r="D50">
-        <v>17022819</v>
+        <v>17021251</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C51">
-        <v>17017912</v>
+        <v>17020590</v>
       </c>
       <c r="D51">
-        <v>17017912</v>
+        <v>17020590</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C52">
-        <v>17055857</v>
+        <v>17052963</v>
       </c>
       <c r="D52">
-        <v>17055857</v>
+        <v>17052963</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C53">
-        <v>17021561</v>
+        <v>17022819</v>
       </c>
       <c r="D53">
-        <v>17021561</v>
+        <v>17022819</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C54">
-        <v>17017165</v>
+        <v>17017912</v>
       </c>
       <c r="D54">
-        <v>17017165</v>
+        <v>17017912</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C55">
-        <v>17020140</v>
+        <v>17055857</v>
       </c>
       <c r="D55">
-        <v>17020140</v>
+        <v>17055857</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C56">
-        <v>17023319</v>
+        <v>17021561</v>
       </c>
       <c r="D56">
-        <v>17023319</v>
+        <v>17021561</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C57">
-        <v>17040051</v>
+        <v>17017165</v>
       </c>
       <c r="D57">
-        <v>17040051</v>
+        <v>17017165</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C58">
-        <v>17021596</v>
+        <v>17020140</v>
       </c>
       <c r="D58">
-        <v>17021596</v>
+        <v>17020140</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C59">
-        <v>17022320</v>
+        <v>17023319</v>
       </c>
       <c r="D59">
-        <v>17022320</v>
+        <v>17023319</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C60">
-        <v>17036917</v>
+        <v>17040051</v>
       </c>
       <c r="D60">
-        <v>17036917</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C61">
-        <v>17021146</v>
+        <v>17021596</v>
       </c>
       <c r="D61">
-        <v>17021146</v>
+        <v>17021596</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C62">
-        <v>17018390</v>
+        <v>17022320</v>
       </c>
       <c r="D62">
-        <v>17018390</v>
+        <v>17022320</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C63">
-        <v>17020581</v>
+        <v>17036917</v>
       </c>
       <c r="D63">
-        <v>17020581</v>
+        <v>17036917</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C64">
-        <v>17022312</v>
+        <v>17021146</v>
       </c>
       <c r="D64">
-        <v>17022312</v>
+        <v>17021146</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C65">
-        <v>17021774</v>
+        <v>17018390</v>
       </c>
       <c r="D65">
-        <v>17021774</v>
+        <v>17018390</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C66">
-        <v>17022339</v>
+        <v>17020581</v>
       </c>
       <c r="D66">
-        <v>17022339</v>
+        <v>17020581</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C67">
-        <v>17040035</v>
+        <v>17022312</v>
       </c>
       <c r="D67">
-        <v>17040035</v>
+        <v>17022312</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C68">
-        <v>17022860</v>
+        <v>17021774</v>
       </c>
       <c r="D68">
-        <v>17022860</v>
+        <v>17021774</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C69">
-        <v>17020611</v>
+        <v>17022339</v>
       </c>
       <c r="D69">
-        <v>17020611</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C70">
-        <v>17021588</v>
+        <v>17040035</v>
       </c>
       <c r="D70">
-        <v>17021588</v>
+        <v>17040035</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C71">
-        <v>17038359</v>
+        <v>17022860</v>
       </c>
       <c r="D71">
-        <v>17038359</v>
+        <v>17022860</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C72">
-        <v>17018404</v>
+        <v>17020611</v>
       </c>
       <c r="D72">
-        <v>17018404</v>
+        <v>17020611</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C73">
-        <v>17021731</v>
+        <v>17021588</v>
       </c>
       <c r="D73">
-        <v>17021731</v>
+        <v>17021588</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C74">
-        <v>17020360</v>
+        <v>17038359</v>
       </c>
       <c r="D74">
-        <v>17020360</v>
+        <v>17038359</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C75">
-        <v>17040841</v>
+        <v>17018404</v>
       </c>
       <c r="D75">
-        <v>17040841</v>
+        <v>17018404</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C76">
-        <v>17020158</v>
+        <v>17021731</v>
       </c>
       <c r="D76">
-        <v>17020158</v>
+        <v>17021731</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C77">
-        <v>17053315</v>
+        <v>17020360</v>
       </c>
       <c r="D77">
-        <v>17053315</v>
+        <v>17020360</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C78">
-        <v>17021600</v>
+        <v>17040841</v>
       </c>
       <c r="D78">
-        <v>17021600</v>
+        <v>17040841</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C79">
-        <v>17017203</v>
+        <v>17020158</v>
       </c>
       <c r="D79">
-        <v>17017203</v>
+        <v>17020158</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C80">
-        <v>17021707</v>
+        <v>17053315</v>
       </c>
       <c r="D80">
-        <v>17021707</v>
+        <v>17053315</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C81">
-        <v>17021804</v>
+        <v>17021600</v>
       </c>
       <c r="D81">
-        <v>17021804</v>
+        <v>17021600</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C82">
-        <v>17106800</v>
+        <v>17017203</v>
       </c>
       <c r="D82">
-        <v>17106800</v>
+        <v>17017203</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C83">
-        <v>17050278</v>
+        <v>17021707</v>
       </c>
       <c r="D83">
-        <v>17050278</v>
+        <v>17021707</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C84">
-        <v>17043069</v>
+        <v>17021804</v>
       </c>
       <c r="D84">
-        <v>17043069</v>
+        <v>17021804</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C85">
-        <v>17018820</v>
+        <v>17106800</v>
       </c>
       <c r="D85">
-        <v>17018820</v>
+        <v>17106800</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C86">
-        <v>17043026</v>
+        <v>17050278</v>
       </c>
       <c r="D86">
-        <v>17043026</v>
+        <v>17050278</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C87">
-        <v>17039150</v>
+        <v>17043069</v>
       </c>
       <c r="D87">
-        <v>17039150</v>
+        <v>17043069</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C88">
-        <v>17052823</v>
+        <v>17018820</v>
       </c>
       <c r="D88">
-        <v>17052823</v>
+        <v>17018820</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C89">
-        <v>17051746</v>
+        <v>17043026</v>
       </c>
       <c r="D89">
-        <v>17051746</v>
+        <v>17043026</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C90">
-        <v>17049253</v>
+        <v>17039150</v>
       </c>
       <c r="D90">
-        <v>17049253</v>
+        <v>17039150</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C91">
+        <v>17052823</v>
+      </c>
+      <c r="D91">
+        <v>17052823</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92">
+        <v>17051746</v>
+      </c>
+      <c r="D92">
+        <v>17051746</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C93">
+        <v>17049253</v>
+      </c>
+      <c r="D93">
+        <v>17049253</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C91">
+      <c r="C94">
         <v>17107806</v>
       </c>
-      <c r="D91">
+      <c r="D94">
         <v>17107806</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="E15" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
     <hyperlink ref="E24" r:id="rId2" xr:uid="{F966175D-36AA-4320-975A-341CC9558720}"/>
@@ -2025,17 +2058,17 @@
     <hyperlink ref="E16" r:id="rId5" xr:uid="{635477EF-96EF-465A-A4D6-2E3AE44588BB}"/>
     <hyperlink ref="E31" r:id="rId6" xr:uid="{D6C9244A-1F4D-4C27-908A-5B7BF77685AE}"/>
     <hyperlink ref="E13" r:id="rId7" xr:uid="{7E3DB7D9-4691-4022-8225-F2D7CFBE3714}"/>
-    <hyperlink ref="E35" r:id="rId8" xr:uid="{32879A96-5C02-40D8-A1E2-148CE6F8505E}"/>
+    <hyperlink ref="E37" r:id="rId8" xr:uid="{32879A96-5C02-40D8-A1E2-148CE6F8505E}"/>
     <hyperlink ref="E21" r:id="rId9" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
     <hyperlink ref="E11" r:id="rId10" xr:uid="{FE6BBF4A-9BA7-4933-95DD-D7EE973277EE}"/>
-    <hyperlink ref="E37" r:id="rId11" xr:uid="{EF0CE8E8-D085-404A-9D31-DD4A973385E7}"/>
+    <hyperlink ref="E40" r:id="rId11" xr:uid="{EF0CE8E8-D085-404A-9D31-DD4A973385E7}"/>
     <hyperlink ref="E8" r:id="rId12" xr:uid="{29C73EBE-F4B7-40A5-8305-373C2D7FECF0}"/>
     <hyperlink ref="E20" r:id="rId13" xr:uid="{41B1E361-F5CC-420C-AB60-F3EF4D081C8D}"/>
     <hyperlink ref="E19" r:id="rId14" xr:uid="{CDEA6D91-661D-4C57-A825-CEAC9F10E5BF}"/>
     <hyperlink ref="E23" r:id="rId15" xr:uid="{6FD4483D-189B-46FB-8558-34F2421D723A}"/>
     <hyperlink ref="E7" r:id="rId16" xr:uid="{4872BBFB-3118-4BD7-8E85-8B56FACEEF91}"/>
     <hyperlink ref="E6" r:id="rId17" xr:uid="{E2A6B184-7479-4337-95C2-FD418B07CCA7}"/>
-    <hyperlink ref="E36" r:id="rId18" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
+    <hyperlink ref="E38" r:id="rId18" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
     <hyperlink ref="E18" r:id="rId19" xr:uid="{4C12CD27-CA4E-42B6-B7D2-981189B38691}"/>
     <hyperlink ref="E2" r:id="rId20" xr:uid="{D6179046-7052-4680-8900-EB813C6718BF}"/>
     <hyperlink ref="E14" r:id="rId21" xr:uid="{08EEA1D1-C096-46B4-87D8-642F20100927}"/>
@@ -2054,8 +2087,10 @@
     <hyperlink ref="E34" r:id="rId34" xr:uid="{A166D7E6-C7B9-4FFC-A5F2-39BCE04F46E2}"/>
     <hyperlink ref="E32" r:id="rId35" xr:uid="{C5EEFE0F-35F9-46FE-979F-AA851E0AEA21}"/>
     <hyperlink ref="E5" r:id="rId36" xr:uid="{3CE5F5C2-354C-436E-8A87-8832048A6DAF}"/>
+    <hyperlink ref="E35" r:id="rId37" xr:uid="{8D967301-E200-4B51-90B0-013BA9341E71}"/>
+    <hyperlink ref="E36" r:id="rId38" xr:uid="{4878822F-4DB3-404F-BC4A-514B8F459B6D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId37"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5978884F-8FA8-491A-8286-B25C38B0C403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB57E2D-1965-4EFC-A68F-8506A4C7361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="174">
   <si>
     <t>CPF</t>
   </si>
@@ -536,6 +536,15 @@
   </si>
   <si>
     <t>alinereis@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>LIDIANE RODRIGUES PEREIRA</t>
+  </si>
+  <si>
+    <t>010.515.591-89</t>
+  </si>
+  <si>
+    <t>lidiane.pereira@professor.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1447,18 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E39" s="2"/>
+      <c r="A39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -2089,8 +2109,9 @@
     <hyperlink ref="E5" r:id="rId36" xr:uid="{3CE5F5C2-354C-436E-8A87-8832048A6DAF}"/>
     <hyperlink ref="E35" r:id="rId37" xr:uid="{8D967301-E200-4B51-90B0-013BA9341E71}"/>
     <hyperlink ref="E36" r:id="rId38" xr:uid="{4878822F-4DB3-404F-BC4A-514B8F459B6D}"/>
+    <hyperlink ref="E39" r:id="rId39" xr:uid="{76019BB8-B2FC-4118-95D2-E1200FED8973}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB57E2D-1965-4EFC-A68F-8506A4C7361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A7D4C2-AECE-4B13-BD39-7191DFDD9996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$95</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="176">
   <si>
     <t>CPF</t>
   </si>
@@ -545,6 +545,12 @@
   </si>
   <si>
     <t>lidiane.pereira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>MARYSTELA LEAL</t>
+  </si>
+  <si>
+    <t>marystelaleal@seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -908,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -1462,614 +1468,622 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>130</v>
-      </c>
-      <c r="B40" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>17021502</v>
       </c>
-      <c r="D41">
+      <c r="D42">
         <v>17021502</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42">
-        <v>17021685</v>
-      </c>
-      <c r="D42">
-        <v>17021685</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
       <c r="D43">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44">
-        <v>17052351</v>
+        <v>17021553</v>
       </c>
       <c r="D44">
-        <v>17052351</v>
+        <v>17021553</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45">
-        <v>17021243</v>
+        <v>17052351</v>
       </c>
       <c r="D45">
-        <v>17021243</v>
+        <v>17052351</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C46">
-        <v>17023181</v>
+        <v>17021243</v>
       </c>
       <c r="D46">
-        <v>17023181</v>
+        <v>17021243</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47">
-        <v>17048826</v>
+        <v>17023181</v>
       </c>
       <c r="D47">
-        <v>17048826</v>
+        <v>17023181</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C48">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
       <c r="D48">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C49">
-        <v>17018382</v>
+        <v>17020336</v>
       </c>
       <c r="D49">
-        <v>17018382</v>
+        <v>17020336</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50">
-        <v>17021251</v>
+        <v>17018382</v>
       </c>
       <c r="D50">
-        <v>17021251</v>
+        <v>17018382</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
       <c r="D51">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52">
-        <v>17052963</v>
+        <v>17020590</v>
       </c>
       <c r="D52">
-        <v>17052963</v>
+        <v>17020590</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C53">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="D53">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C54">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="D54">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="D55">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56">
-        <v>17021561</v>
+        <v>17055857</v>
       </c>
       <c r="D56">
-        <v>17021561</v>
+        <v>17055857</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57">
-        <v>17017165</v>
+        <v>17021561</v>
       </c>
       <c r="D57">
-        <v>17017165</v>
+        <v>17021561</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="D58">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C59">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="D59">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C60">
-        <v>17040051</v>
+        <v>17023319</v>
       </c>
       <c r="D60">
-        <v>17040051</v>
+        <v>17023319</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C61">
-        <v>17021596</v>
+        <v>17040051</v>
       </c>
       <c r="D61">
-        <v>17021596</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C62">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="D62">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C63">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="D63">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C64">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="D64">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C65">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="D65">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C66">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="D66">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="D67">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C68">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="D68">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C69">
-        <v>17022339</v>
+        <v>17021774</v>
       </c>
       <c r="D69">
-        <v>17022339</v>
+        <v>17021774</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C70">
-        <v>17040035</v>
+        <v>17022339</v>
       </c>
       <c r="D70">
-        <v>17040035</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="D71">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C72">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="D72">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="D73">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C74">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="D74">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C75">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="D75">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C76">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="D76">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C77">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="D77">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C78">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="D78">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C79">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="D79">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C80">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="D80">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C81">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="D81">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C82">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="D82">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C83">
-        <v>17021707</v>
+        <v>17017203</v>
       </c>
       <c r="D83">
-        <v>17021707</v>
+        <v>17017203</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C84">
-        <v>17021804</v>
+        <v>17021707</v>
       </c>
       <c r="D84">
-        <v>17021804</v>
+        <v>17021707</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="D85">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C86">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="D86">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C87">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="D87">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C88">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="D88">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C89">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="D89">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C90">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="D90">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C91">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="D91">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C92">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="D92">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C93">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="D93">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94">
+        <v>17049253</v>
+      </c>
+      <c r="D94">
+        <v>17049253</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C94">
+      <c r="C95">
         <v>17107806</v>
       </c>
-      <c r="D94">
+      <c r="D95">
         <v>17107806</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="E15" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
     <hyperlink ref="E24" r:id="rId2" xr:uid="{F966175D-36AA-4320-975A-341CC9558720}"/>
@@ -2081,7 +2095,7 @@
     <hyperlink ref="E37" r:id="rId8" xr:uid="{32879A96-5C02-40D8-A1E2-148CE6F8505E}"/>
     <hyperlink ref="E21" r:id="rId9" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
     <hyperlink ref="E11" r:id="rId10" xr:uid="{FE6BBF4A-9BA7-4933-95DD-D7EE973277EE}"/>
-    <hyperlink ref="E40" r:id="rId11" xr:uid="{EF0CE8E8-D085-404A-9D31-DD4A973385E7}"/>
+    <hyperlink ref="E41" r:id="rId11" xr:uid="{EF0CE8E8-D085-404A-9D31-DD4A973385E7}"/>
     <hyperlink ref="E8" r:id="rId12" xr:uid="{29C73EBE-F4B7-40A5-8305-373C2D7FECF0}"/>
     <hyperlink ref="E20" r:id="rId13" xr:uid="{41B1E361-F5CC-420C-AB60-F3EF4D081C8D}"/>
     <hyperlink ref="E19" r:id="rId14" xr:uid="{CDEA6D91-661D-4C57-A825-CEAC9F10E5BF}"/>
@@ -2110,8 +2124,9 @@
     <hyperlink ref="E35" r:id="rId37" xr:uid="{8D967301-E200-4B51-90B0-013BA9341E71}"/>
     <hyperlink ref="E36" r:id="rId38" xr:uid="{4878822F-4DB3-404F-BC4A-514B8F459B6D}"/>
     <hyperlink ref="E39" r:id="rId39" xr:uid="{76019BB8-B2FC-4118-95D2-E1200FED8973}"/>
+    <hyperlink ref="E40" r:id="rId40" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A7D4C2-AECE-4B13-BD39-7191DFDD9996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DB48E2-1A70-4BAC-9CA3-14AAD7B71D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="177">
   <si>
     <t>CPF</t>
   </si>
@@ -551,6 +551,9 @@
   </si>
   <si>
     <t>marystelaleal@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>waldirlins@ue.seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -595,10 +598,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1917,7 +1923,7 @@
         <v>17020158</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>96</v>
       </c>
@@ -1928,7 +1934,7 @@
         <v>17053315</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>97</v>
       </c>
@@ -1939,7 +1945,7 @@
         <v>17021600</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>98</v>
       </c>
@@ -1950,7 +1956,7 @@
         <v>17017203</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>99</v>
       </c>
@@ -1960,8 +1966,11 @@
       <c r="D84">
         <v>17021707</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>100</v>
       </c>
@@ -1972,7 +1981,7 @@
         <v>17021804</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>101</v>
       </c>
@@ -1983,7 +1992,7 @@
         <v>17106800</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>102</v>
       </c>
@@ -1994,7 +2003,7 @@
         <v>17050278</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -2005,7 +2014,7 @@
         <v>17043069</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>104</v>
       </c>
@@ -2016,7 +2025,7 @@
         <v>17018820</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>105</v>
       </c>
@@ -2027,7 +2036,7 @@
         <v>17043026</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>106</v>
       </c>
@@ -2038,7 +2047,7 @@
         <v>17039150</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>107</v>
       </c>
@@ -2049,7 +2058,7 @@
         <v>17052823</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>108</v>
       </c>
@@ -2060,7 +2069,7 @@
         <v>17051746</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>109</v>
       </c>
@@ -2071,7 +2080,7 @@
         <v>17049253</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>110</v>
       </c>
@@ -2125,8 +2134,9 @@
     <hyperlink ref="E36" r:id="rId38" xr:uid="{4878822F-4DB3-404F-BC4A-514B8F459B6D}"/>
     <hyperlink ref="E39" r:id="rId39" xr:uid="{76019BB8-B2FC-4118-95D2-E1200FED8973}"/>
     <hyperlink ref="E40" r:id="rId40" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
+    <hyperlink ref="E84" r:id="rId41" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DB48E2-1A70-4BAC-9CA3-14AAD7B71D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2971FA6-F2DC-4F72-B91D-7D1819029A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="178">
   <si>
     <t>CPF</t>
   </si>
@@ -554,6 +554,9 @@
   </si>
   <si>
     <t>waldirlins@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>alvorada@ue.seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -1571,7 +1574,7 @@
         <v>17048826</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>66</v>
       </c>
@@ -1582,7 +1585,7 @@
         <v>17020336</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>67</v>
       </c>
@@ -1593,7 +1596,7 @@
         <v>17018382</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>68</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>17021251</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>69</v>
       </c>
@@ -1614,8 +1617,11 @@
       <c r="D52">
         <v>17020590</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>70</v>
       </c>
@@ -1626,7 +1632,7 @@
         <v>17052963</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>71</v>
       </c>
@@ -1637,7 +1643,7 @@
         <v>17022819</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>72</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>17017912</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>73</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>17055857</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>74</v>
       </c>
@@ -1670,7 +1676,7 @@
         <v>17021561</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>75</v>
       </c>
@@ -1681,7 +1687,7 @@
         <v>17017165</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>76</v>
       </c>
@@ -1692,7 +1698,7 @@
         <v>17020140</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>115</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>17023319</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>77</v>
       </c>
@@ -1714,7 +1720,7 @@
         <v>17040051</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>78</v>
       </c>
@@ -1725,7 +1731,7 @@
         <v>17021596</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>79</v>
       </c>
@@ -1736,7 +1742,7 @@
         <v>17022320</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>80</v>
       </c>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2971FA6-F2DC-4F72-B91D-7D1819029A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A64621-C8BB-43D2-8E86-C4B39688DF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="226">
   <si>
     <t>CPF</t>
   </si>
@@ -557,13 +557,169 @@
   </si>
   <si>
     <t>alvorada@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>aryribeirovaladaofilho@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>gurupi@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomjesus@ue.seduc.to.gov.br </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> alairsena@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaidesoares@ue.seduc.to.gov.br </t>
+  </si>
+  <si>
+    <t>anitamoreno@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>positivogurupi@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>reginacampos@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beneditobandeira@seduc.to.gov.br   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">candidofigueira@ue.seduc.to.gov.br  </t>
+  </si>
+  <si>
+    <t>talisma@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>domalano@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>elesbaolima@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>colegiojoseporfirio@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>joseseabralemos@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>joaotavares@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>tiradentes@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>nsaparecida@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>sucupira@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>professoramoura@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>tarsodutra@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>adjuliobalthazar@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolamariaguedes@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>presidentecostaesilva@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>izaelaraujojb@gmail.com</t>
+  </si>
+  <si>
+    <t>tancredodealmeida@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>anamaria@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>joaquimcosta@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>fealegria@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>gercinateixeira@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>herciliasilva@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>senhoradocarmo@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>crixas@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>pejoseanchieta@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>passoapasso@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>instpresbaraguaia@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>wesleiferreira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>vilaguaracy@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolaindigena_b@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolaindigena_ijanari@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolaindigena_taina@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolaindigena_ijawala@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>robertosilvajunior@professor.to.gov.br</t>
+  </si>
+  <si>
+    <r>
+      <t>escolaindigena_temanare@ue.seduc.to.gov.br</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>escolaindigena_tewadure@ue.seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>hina@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>escolaindigena_wahuri@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escolaindigena_watakuri@ue.seduc.to.gov.br </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -578,6 +734,13 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -601,13 +764,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1507,6 +1671,9 @@
       <c r="D42">
         <v>17021502</v>
       </c>
+      <c r="E42" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -1518,6 +1685,9 @@
       <c r="D43">
         <v>17021685</v>
       </c>
+      <c r="E43" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -1529,6 +1699,9 @@
       <c r="D44">
         <v>17021553</v>
       </c>
+      <c r="E44" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -1540,6 +1713,7 @@
       <c r="D45">
         <v>17052351</v>
       </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -1551,6 +1725,9 @@
       <c r="D46">
         <v>17021243</v>
       </c>
+      <c r="E46" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -1562,6 +1739,7 @@
       <c r="D47">
         <v>17023181</v>
       </c>
+      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -1573,6 +1751,9 @@
       <c r="D48">
         <v>17048826</v>
       </c>
+      <c r="E48" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -1584,6 +1765,9 @@
       <c r="D49">
         <v>17020336</v>
       </c>
+      <c r="E49" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
@@ -1595,6 +1779,9 @@
       <c r="D50">
         <v>17018382</v>
       </c>
+      <c r="E50" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -1606,6 +1793,9 @@
       <c r="D51">
         <v>17021251</v>
       </c>
+      <c r="E51" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
@@ -1631,6 +1821,9 @@
       <c r="D53">
         <v>17052963</v>
       </c>
+      <c r="E53" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -1642,6 +1835,9 @@
       <c r="D54">
         <v>17022819</v>
       </c>
+      <c r="E54" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
@@ -1653,6 +1849,9 @@
       <c r="D55">
         <v>17017912</v>
       </c>
+      <c r="E55" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
@@ -1664,6 +1863,9 @@
       <c r="D56">
         <v>17055857</v>
       </c>
+      <c r="E56" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
@@ -1675,6 +1877,9 @@
       <c r="D57">
         <v>17021561</v>
       </c>
+      <c r="E57" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
@@ -1686,6 +1891,9 @@
       <c r="D58">
         <v>17017165</v>
       </c>
+      <c r="E58" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
@@ -1697,6 +1905,9 @@
       <c r="D59">
         <v>17020140</v>
       </c>
+      <c r="E59" s="2" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -1708,6 +1919,9 @@
       <c r="D60">
         <v>17023319</v>
       </c>
+      <c r="E60" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -1730,6 +1944,9 @@
       <c r="D62">
         <v>17021596</v>
       </c>
+      <c r="E62" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
@@ -1741,6 +1958,9 @@
       <c r="D63">
         <v>17022320</v>
       </c>
+      <c r="E63" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
@@ -1752,8 +1972,11 @@
       <c r="D64">
         <v>17036917</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>81</v>
       </c>
@@ -1763,8 +1986,11 @@
       <c r="D65">
         <v>17021146</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>82</v>
       </c>
@@ -1774,8 +2000,11 @@
       <c r="D66">
         <v>17018390</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>83</v>
       </c>
@@ -1785,8 +2014,11 @@
       <c r="D67">
         <v>17020581</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>84</v>
       </c>
@@ -1796,8 +2028,11 @@
       <c r="D68">
         <v>17022312</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>85</v>
       </c>
@@ -1807,8 +2042,11 @@
       <c r="D69">
         <v>17021774</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>86</v>
       </c>
@@ -1819,7 +2057,7 @@
         <v>17022339</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>87</v>
       </c>
@@ -1829,8 +2067,11 @@
       <c r="D71">
         <v>17040035</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>88</v>
       </c>
@@ -1840,8 +2081,11 @@
       <c r="D72">
         <v>17022860</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>89</v>
       </c>
@@ -1851,8 +2095,11 @@
       <c r="D73">
         <v>17020611</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>90</v>
       </c>
@@ -1862,8 +2109,11 @@
       <c r="D74">
         <v>17021588</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>91</v>
       </c>
@@ -1873,8 +2123,11 @@
       <c r="D75">
         <v>17038359</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>92</v>
       </c>
@@ -1884,8 +2137,11 @@
       <c r="D76">
         <v>17018404</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>93</v>
       </c>
@@ -1895,8 +2151,11 @@
       <c r="D77">
         <v>17021731</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>94</v>
       </c>
@@ -1906,8 +2165,11 @@
       <c r="D78">
         <v>17020360</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>112</v>
       </c>
@@ -1917,8 +2179,11 @@
       <c r="D79">
         <v>17040841</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>95</v>
       </c>
@@ -1927,6 +2192,9 @@
       </c>
       <c r="D80">
         <v>17020158</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -1939,6 +2207,9 @@
       <c r="D81">
         <v>17053315</v>
       </c>
+      <c r="E81" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
@@ -1950,6 +2221,9 @@
       <c r="D82">
         <v>17021600</v>
       </c>
+      <c r="E82" s="2" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
@@ -1961,6 +2235,9 @@
       <c r="D83">
         <v>17017203</v>
       </c>
+      <c r="E83" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
@@ -1986,6 +2263,9 @@
       <c r="D85">
         <v>17021804</v>
       </c>
+      <c r="E85" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -1997,6 +2277,9 @@
       <c r="D86">
         <v>17106800</v>
       </c>
+      <c r="E86" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
@@ -2008,6 +2291,9 @@
       <c r="D87">
         <v>17050278</v>
       </c>
+      <c r="E87" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
@@ -2019,6 +2305,9 @@
       <c r="D88">
         <v>17043069</v>
       </c>
+      <c r="E88" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
@@ -2030,6 +2319,9 @@
       <c r="D89">
         <v>17018820</v>
       </c>
+      <c r="E89" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
@@ -2041,6 +2333,9 @@
       <c r="D90">
         <v>17043026</v>
       </c>
+      <c r="E90" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
@@ -2052,6 +2347,9 @@
       <c r="D91">
         <v>17039150</v>
       </c>
+      <c r="E91" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
@@ -2063,6 +2361,9 @@
       <c r="D92">
         <v>17052823</v>
       </c>
+      <c r="E92" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
@@ -2074,6 +2375,9 @@
       <c r="D93">
         <v>17051746</v>
       </c>
+      <c r="E93" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -2085,6 +2389,9 @@
       <c r="D94">
         <v>17049253</v>
       </c>
+      <c r="E94" s="2" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
@@ -2095,6 +2402,9 @@
       </c>
       <c r="D95">
         <v>17107806</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2141,8 +2451,50 @@
     <hyperlink ref="E39" r:id="rId39" xr:uid="{76019BB8-B2FC-4118-95D2-E1200FED8973}"/>
     <hyperlink ref="E40" r:id="rId40" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
     <hyperlink ref="E84" r:id="rId41" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
+    <hyperlink ref="E42" r:id="rId42" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
+    <hyperlink ref="E43" r:id="rId43" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
+    <hyperlink ref="E44" r:id="rId44" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
+    <hyperlink ref="E48" r:id="rId45" xr:uid="{456736E6-F5EC-4F85-8E29-563F7384B7FC}"/>
+    <hyperlink ref="E49" r:id="rId46" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
+    <hyperlink ref="E50" r:id="rId47" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
+    <hyperlink ref="E51" r:id="rId48" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
+    <hyperlink ref="E53" r:id="rId49" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
+    <hyperlink ref="E56" r:id="rId50" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
+    <hyperlink ref="E58" r:id="rId51" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
+    <hyperlink ref="E59" r:id="rId52" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
+    <hyperlink ref="E60" r:id="rId53" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
+    <hyperlink ref="E63" r:id="rId54" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
+    <hyperlink ref="E64" r:id="rId55" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
+    <hyperlink ref="E65" r:id="rId56" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
+    <hyperlink ref="E66" r:id="rId57" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
+    <hyperlink ref="E67" r:id="rId58" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
+    <hyperlink ref="E68" r:id="rId59" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
+    <hyperlink ref="E69" r:id="rId60" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
+    <hyperlink ref="E71" r:id="rId61" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
+    <hyperlink ref="E73" r:id="rId62" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
+    <hyperlink ref="E74" r:id="rId63" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
+    <hyperlink ref="E75" r:id="rId64" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
+    <hyperlink ref="E76" r:id="rId65" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
+    <hyperlink ref="E77" r:id="rId66" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
+    <hyperlink ref="E78" r:id="rId67" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
+    <hyperlink ref="E79" r:id="rId68" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
+    <hyperlink ref="E80" r:id="rId69" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
+    <hyperlink ref="E81" r:id="rId70" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
+    <hyperlink ref="E82" r:id="rId71" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
+    <hyperlink ref="E83" r:id="rId72" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
+    <hyperlink ref="E85" r:id="rId73" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
+    <hyperlink ref="E86" r:id="rId74" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
+    <hyperlink ref="E87" r:id="rId75" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
+    <hyperlink ref="E88" r:id="rId76" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
+    <hyperlink ref="E89" r:id="rId77" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
+    <hyperlink ref="E90" r:id="rId78" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
+    <hyperlink ref="E91" r:id="rId79" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
+    <hyperlink ref="E92" r:id="rId80" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
+    <hyperlink ref="E93" r:id="rId81" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
+    <hyperlink ref="E94" r:id="rId82" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
+    <hyperlink ref="E95" r:id="rId83" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId84"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A64621-C8BB-43D2-8E86-C4B39688DF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D23570-7007-43E2-929E-19B239EFE5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="227">
   <si>
     <t>CPF</t>
   </si>
@@ -713,6 +713,9 @@
   </si>
   <si>
     <t xml:space="preserve">escolaindigena_watakuri@ue.seduc.to.gov.br </t>
+  </si>
+  <si>
+    <t>planejamentoscea@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -1807,608 +1810,622 @@
       <c r="D52">
         <v>17020590</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>177</v>
+      <c r="E52" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53">
-        <v>17052963</v>
+        <v>17020590</v>
       </c>
       <c r="D53">
-        <v>17052963</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>188</v>
+        <v>17020590</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C54">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="D54">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C55">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="D55">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C56">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="D56">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C57">
-        <v>17021561</v>
+        <v>17055857</v>
       </c>
       <c r="D57">
-        <v>17021561</v>
-      </c>
-      <c r="E57" t="s">
-        <v>192</v>
+        <v>17055857</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C58">
-        <v>17017165</v>
+        <v>17021561</v>
       </c>
       <c r="D58">
-        <v>17017165</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>193</v>
+        <v>17021561</v>
+      </c>
+      <c r="E58" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C59">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="D59">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C60">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="D60">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C61">
-        <v>17040051</v>
+        <v>17023319</v>
       </c>
       <c r="D61">
-        <v>17040051</v>
+        <v>17023319</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62">
-        <v>17021596</v>
+        <v>17040051</v>
       </c>
       <c r="D62">
-        <v>17021596</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>184</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="D63">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="D64">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="D65">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="D66">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C67">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="D67">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="D68">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C69">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="D69">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C70">
-        <v>17022339</v>
+        <v>17021774</v>
       </c>
       <c r="D70">
-        <v>17022339</v>
+        <v>17021774</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71">
-        <v>17040035</v>
+        <v>17022339</v>
       </c>
       <c r="D71">
-        <v>17040035</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>202</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="D72">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="D73">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C74">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="D74">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C75">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="D75">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C76">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="D76">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="D77">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C78">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="D78">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C79">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="D79">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C80">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="D80">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C81">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="D81">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C82">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="D82">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C83">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="D83">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C84">
-        <v>17021707</v>
+        <v>17017203</v>
       </c>
       <c r="D84">
-        <v>17021707</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>176</v>
+        <v>17017203</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C85">
-        <v>17021804</v>
+        <v>17021707</v>
       </c>
       <c r="D85">
-        <v>17021804</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>215</v>
+        <v>17021707</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="D86">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C87">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="D87">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C88">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="D88">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C89">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="D89">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C90">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="D90">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C91">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="D91">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C92">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="D92">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C93">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="D93">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C94">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="D94">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C95">
+        <v>17049253</v>
+      </c>
+      <c r="D95">
+        <v>17049253</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C95">
+      <c r="C96">
         <v>17107806</v>
       </c>
-      <c r="D95">
+      <c r="D96">
         <v>17107806</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>225</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="E15" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
     <hyperlink ref="E24" r:id="rId2" xr:uid="{F966175D-36AA-4320-975A-341CC9558720}"/>
@@ -2450,7 +2467,7 @@
     <hyperlink ref="E36" r:id="rId38" xr:uid="{4878822F-4DB3-404F-BC4A-514B8F459B6D}"/>
     <hyperlink ref="E39" r:id="rId39" xr:uid="{76019BB8-B2FC-4118-95D2-E1200FED8973}"/>
     <hyperlink ref="E40" r:id="rId40" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
-    <hyperlink ref="E84" r:id="rId41" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
+    <hyperlink ref="E85" r:id="rId41" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
     <hyperlink ref="E42" r:id="rId42" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
     <hyperlink ref="E43" r:id="rId43" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
     <hyperlink ref="E44" r:id="rId44" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
@@ -2458,43 +2475,44 @@
     <hyperlink ref="E49" r:id="rId46" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
     <hyperlink ref="E50" r:id="rId47" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
     <hyperlink ref="E51" r:id="rId48" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
-    <hyperlink ref="E53" r:id="rId49" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
-    <hyperlink ref="E56" r:id="rId50" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
-    <hyperlink ref="E58" r:id="rId51" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
-    <hyperlink ref="E59" r:id="rId52" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
-    <hyperlink ref="E60" r:id="rId53" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
-    <hyperlink ref="E63" r:id="rId54" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
-    <hyperlink ref="E64" r:id="rId55" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
-    <hyperlink ref="E65" r:id="rId56" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
-    <hyperlink ref="E66" r:id="rId57" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
-    <hyperlink ref="E67" r:id="rId58" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
-    <hyperlink ref="E68" r:id="rId59" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
-    <hyperlink ref="E69" r:id="rId60" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
-    <hyperlink ref="E71" r:id="rId61" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
-    <hyperlink ref="E73" r:id="rId62" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
-    <hyperlink ref="E74" r:id="rId63" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
-    <hyperlink ref="E75" r:id="rId64" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
-    <hyperlink ref="E76" r:id="rId65" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
-    <hyperlink ref="E77" r:id="rId66" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
-    <hyperlink ref="E78" r:id="rId67" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
-    <hyperlink ref="E79" r:id="rId68" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
-    <hyperlink ref="E80" r:id="rId69" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
-    <hyperlink ref="E81" r:id="rId70" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
-    <hyperlink ref="E82" r:id="rId71" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
-    <hyperlink ref="E83" r:id="rId72" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
-    <hyperlink ref="E85" r:id="rId73" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
-    <hyperlink ref="E86" r:id="rId74" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
-    <hyperlink ref="E87" r:id="rId75" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
-    <hyperlink ref="E88" r:id="rId76" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
-    <hyperlink ref="E89" r:id="rId77" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
-    <hyperlink ref="E90" r:id="rId78" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
-    <hyperlink ref="E91" r:id="rId79" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
-    <hyperlink ref="E92" r:id="rId80" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
-    <hyperlink ref="E93" r:id="rId81" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
-    <hyperlink ref="E94" r:id="rId82" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
-    <hyperlink ref="E95" r:id="rId83" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
+    <hyperlink ref="E54" r:id="rId49" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
+    <hyperlink ref="E57" r:id="rId50" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
+    <hyperlink ref="E59" r:id="rId51" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
+    <hyperlink ref="E60" r:id="rId52" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
+    <hyperlink ref="E61" r:id="rId53" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
+    <hyperlink ref="E64" r:id="rId54" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
+    <hyperlink ref="E65" r:id="rId55" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
+    <hyperlink ref="E66" r:id="rId56" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
+    <hyperlink ref="E67" r:id="rId57" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
+    <hyperlink ref="E68" r:id="rId58" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
+    <hyperlink ref="E69" r:id="rId59" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
+    <hyperlink ref="E70" r:id="rId60" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
+    <hyperlink ref="E72" r:id="rId61" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
+    <hyperlink ref="E74" r:id="rId62" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
+    <hyperlink ref="E75" r:id="rId63" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
+    <hyperlink ref="E76" r:id="rId64" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
+    <hyperlink ref="E77" r:id="rId65" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
+    <hyperlink ref="E78" r:id="rId66" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
+    <hyperlink ref="E79" r:id="rId67" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
+    <hyperlink ref="E80" r:id="rId68" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
+    <hyperlink ref="E81" r:id="rId69" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
+    <hyperlink ref="E82" r:id="rId70" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
+    <hyperlink ref="E83" r:id="rId71" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
+    <hyperlink ref="E84" r:id="rId72" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
+    <hyperlink ref="E86" r:id="rId73" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
+    <hyperlink ref="E87" r:id="rId74" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
+    <hyperlink ref="E88" r:id="rId75" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
+    <hyperlink ref="E89" r:id="rId76" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
+    <hyperlink ref="E90" r:id="rId77" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
+    <hyperlink ref="E91" r:id="rId78" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
+    <hyperlink ref="E92" r:id="rId79" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
+    <hyperlink ref="E93" r:id="rId80" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
+    <hyperlink ref="E94" r:id="rId81" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
+    <hyperlink ref="E95" r:id="rId82" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
+    <hyperlink ref="E96" r:id="rId83" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
+    <hyperlink ref="E52" r:id="rId84" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId84"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D23570-7007-43E2-929E-19B239EFE5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB486F7A-5066-4336-8AC2-851D51BF3880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="229">
   <si>
     <t>CPF</t>
   </si>
@@ -716,6 +716,12 @@
   </si>
   <si>
     <t>planejamentoscea@gmail.com</t>
+  </si>
+  <si>
+    <t>RENATO MACHADO</t>
+  </si>
+  <si>
+    <t>renatofmachado2023@professor.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -2422,6 +2428,14 @@
       </c>
       <c r="E96" s="2" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -2511,8 +2525,9 @@
     <hyperlink ref="E95" r:id="rId82" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
     <hyperlink ref="E96" r:id="rId83" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
     <hyperlink ref="E52" r:id="rId84" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
+    <hyperlink ref="E97" r:id="rId85" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId86"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB486F7A-5066-4336-8AC2-851D51BF3880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91682AAF-7DFC-472F-A277-A98F046F8F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="231">
   <si>
     <t>CPF</t>
   </si>
@@ -722,6 +722,12 @@
   </si>
   <si>
     <t>renatofmachado2023@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ROBERTA LUZ SILVA</t>
+  </si>
+  <si>
+    <t>roberta.silva@seduc.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -2436,6 +2442,14 @@
       </c>
       <c r="E97" s="2" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2526,8 +2540,9 @@
     <hyperlink ref="E96" r:id="rId83" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
     <hyperlink ref="E52" r:id="rId84" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
     <hyperlink ref="E97" r:id="rId85" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
+    <hyperlink ref="E98" r:id="rId86" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId86"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D48C37-FB49-4A6B-ADB1-FABBFF59DE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Modulações Administrativas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modulações Administrativas'!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
   <si>
     <t>CPF</t>
   </si>
@@ -473,6 +473,15 @@
   </si>
   <si>
     <t>roberta.silva@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>ALLINE LEMOS LIRA</t>
+  </si>
+  <si>
+    <t>033.867.511-64</t>
+  </si>
+  <si>
+    <t>alline.lira@professor.to.gov.br</t>
   </si>
 </sst>
 </file>
@@ -847,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -945,230 +954,230 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>17021502</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>17021502</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>17021685</v>
-      </c>
-      <c r="D14">
-        <v>17021685</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
       <c r="D15">
-        <v>17021553</v>
+        <v>17021685</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>17052351</v>
+        <v>17021553</v>
       </c>
       <c r="D16">
-        <v>17052351</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>17021553</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>17021243</v>
+        <v>17052351</v>
       </c>
       <c r="D17">
-        <v>17021243</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>17052351</v>
+      </c>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>17023181</v>
+        <v>17021243</v>
       </c>
       <c r="D18">
-        <v>17023181</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>17021243</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>17048826</v>
+        <v>17023181</v>
       </c>
       <c r="D19">
-        <v>17048826</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>17023181</v>
+      </c>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
       <c r="D20">
-        <v>17020336</v>
+        <v>17048826</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>17018382</v>
+        <v>17020336</v>
       </c>
       <c r="D21">
-        <v>17018382</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>17020336</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
-        <v>17021251</v>
+        <v>17018382</v>
       </c>
       <c r="D22">
-        <v>17021251</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>102</v>
+        <v>17018382</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
       <c r="D23">
-        <v>17020590</v>
+        <v>17021251</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,684 +1190,699 @@
       <c r="D24">
         <v>17020590</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
+      <c r="E24" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>17052963</v>
+        <v>17020590</v>
       </c>
       <c r="D25">
-        <v>17052963</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>103</v>
+        <v>17020590</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="D26">
-        <v>17022819</v>
+        <v>17052963</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="D27">
-        <v>17017912</v>
+        <v>17022819</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="D28">
-        <v>17055857</v>
+        <v>17017912</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>17021561</v>
+        <v>17055857</v>
       </c>
       <c r="D29">
-        <v>17021561</v>
-      </c>
-      <c r="E29" t="s">
-        <v>107</v>
+        <v>17055857</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>17017165</v>
+        <v>17021561</v>
       </c>
       <c r="D30">
-        <v>17017165</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>17021561</v>
+      </c>
+      <c r="E30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="D31">
-        <v>17020140</v>
+        <v>17017165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="D32">
-        <v>17023319</v>
+        <v>17020140</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C33">
-        <v>17040051</v>
+        <v>17023319</v>
       </c>
       <c r="D33">
-        <v>17040051</v>
+        <v>17023319</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34">
-        <v>17021596</v>
+        <v>17040051</v>
       </c>
       <c r="D34">
-        <v>17021596</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>17040051</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="D35">
-        <v>17022320</v>
+        <v>17021596</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="D36">
-        <v>17036917</v>
+        <v>17022320</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="D37">
-        <v>17021146</v>
+        <v>17036917</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="D38">
-        <v>17018390</v>
+        <v>17021146</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="D39">
-        <v>17020581</v>
+        <v>17018390</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="D40">
-        <v>17022312</v>
+        <v>17020581</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="D41">
-        <v>17021774</v>
+        <v>17022312</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
-        <v>17022339</v>
+        <v>17021774</v>
       </c>
       <c r="D42">
-        <v>17022339</v>
+        <v>17021774</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
-        <v>17040035</v>
+        <v>17022339</v>
       </c>
       <c r="D43">
-        <v>17040035</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>17022339</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="D44">
-        <v>17022860</v>
+        <v>17040035</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="D45">
-        <v>17020611</v>
+        <v>17022860</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="D46">
-        <v>17021588</v>
+        <v>17020611</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="D47">
-        <v>17038359</v>
+        <v>17021588</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="D48">
-        <v>17018404</v>
+        <v>17038359</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="D49">
-        <v>17021731</v>
+        <v>17018404</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="D50">
-        <v>17020360</v>
+        <v>17021731</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C51">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="D51">
-        <v>17040841</v>
+        <v>17020360</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C52">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="D52">
-        <v>17020158</v>
+        <v>17040841</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="D53">
-        <v>17053315</v>
+        <v>17020158</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="D54">
-        <v>17021600</v>
+        <v>17053315</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="D55">
-        <v>17017203</v>
+        <v>17021600</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56">
-        <v>17021707</v>
+        <v>17017203</v>
       </c>
       <c r="D56">
-        <v>17021707</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>91</v>
+        <v>17017203</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57">
-        <v>17021804</v>
+        <v>17021707</v>
       </c>
       <c r="D57">
-        <v>17021804</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>130</v>
+        <v>17021707</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C58">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="D58">
-        <v>17106800</v>
+        <v>17021804</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="D59">
-        <v>17050278</v>
+        <v>17106800</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="D60">
-        <v>17043069</v>
+        <v>17050278</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="D61">
-        <v>17018820</v>
+        <v>17043069</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="D62">
-        <v>17043026</v>
+        <v>17018820</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C63">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="D63">
-        <v>17039150</v>
+        <v>17043026</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="D64">
-        <v>17052823</v>
+        <v>17039150</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="D65">
-        <v>17051746</v>
+        <v>17052823</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="D66">
-        <v>17049253</v>
+        <v>17051746</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67">
-        <v>17107806</v>
+        <v>17049253</v>
       </c>
       <c r="D67">
-        <v>17107806</v>
+        <v>17049253</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
+      </c>
+      <c r="C68">
+        <v>17107806</v>
+      </c>
+      <c r="D68">
+        <v>17107806</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{AEE0C3B0-1BF3-48EB-9EA3-5A746517858E}"/>
     <hyperlink ref="E5" r:id="rId2" xr:uid="{FFA4987F-29BF-4F74-8419-9416FABC6C69}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{9FFBE38D-6766-404F-9093-B70ECCCB57C6}"/>
     <hyperlink ref="E4" r:id="rId4" xr:uid="{29C73EBE-F4B7-40A5-8305-373C2D7FECF0}"/>
     <hyperlink ref="E3" r:id="rId5" xr:uid="{E2A6B184-7479-4337-95C2-FD418B07CCA7}"/>
-    <hyperlink ref="E11" r:id="rId6" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
-    <hyperlink ref="E9" r:id="rId7" xr:uid="{B3D75A10-03B2-4F9C-825A-1B5499F96C0C}"/>
-    <hyperlink ref="E10" r:id="rId8" xr:uid="{CEAEB9FE-B633-4EAD-B5BE-4CC1F7E94580}"/>
+    <hyperlink ref="E12" r:id="rId6" xr:uid="{D01EFA09-D00A-446D-9CBF-BA11FA44A974}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{B3D75A10-03B2-4F9C-825A-1B5499F96C0C}"/>
+    <hyperlink ref="E11" r:id="rId8" xr:uid="{CEAEB9FE-B633-4EAD-B5BE-4CC1F7E94580}"/>
     <hyperlink ref="E2" r:id="rId9" xr:uid="{A47CB573-E728-4F1D-BEE9-F780733C389C}"/>
     <hyperlink ref="E6" r:id="rId10" xr:uid="{AFA83F14-A689-43A6-855D-6CCFA729507F}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
-    <hyperlink ref="E56" r:id="rId12" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
-    <hyperlink ref="E13" r:id="rId13" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
-    <hyperlink ref="E14" r:id="rId14" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
-    <hyperlink ref="E15" r:id="rId15" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
-    <hyperlink ref="E19" r:id="rId16" xr:uid="{456736E6-F5EC-4F85-8E29-563F7384B7FC}"/>
-    <hyperlink ref="E20" r:id="rId17" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
-    <hyperlink ref="E21" r:id="rId18" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
-    <hyperlink ref="E22" r:id="rId19" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
-    <hyperlink ref="E25" r:id="rId20" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
-    <hyperlink ref="E28" r:id="rId21" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
-    <hyperlink ref="E30" r:id="rId22" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
-    <hyperlink ref="E31" r:id="rId23" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
-    <hyperlink ref="E32" r:id="rId24" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
-    <hyperlink ref="E35" r:id="rId25" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
-    <hyperlink ref="E36" r:id="rId26" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
-    <hyperlink ref="E37" r:id="rId27" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
-    <hyperlink ref="E38" r:id="rId28" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
-    <hyperlink ref="E39" r:id="rId29" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
-    <hyperlink ref="E40" r:id="rId30" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
-    <hyperlink ref="E41" r:id="rId31" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
-    <hyperlink ref="E43" r:id="rId32" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
-    <hyperlink ref="E45" r:id="rId33" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
-    <hyperlink ref="E46" r:id="rId34" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
-    <hyperlink ref="E47" r:id="rId35" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
-    <hyperlink ref="E48" r:id="rId36" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
-    <hyperlink ref="E49" r:id="rId37" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
-    <hyperlink ref="E50" r:id="rId38" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
-    <hyperlink ref="E51" r:id="rId39" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
-    <hyperlink ref="E52" r:id="rId40" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
-    <hyperlink ref="E53" r:id="rId41" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
-    <hyperlink ref="E54" r:id="rId42" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
-    <hyperlink ref="E55" r:id="rId43" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
-    <hyperlink ref="E57" r:id="rId44" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
-    <hyperlink ref="E58" r:id="rId45" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
-    <hyperlink ref="E59" r:id="rId46" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
-    <hyperlink ref="E60" r:id="rId47" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
-    <hyperlink ref="E61" r:id="rId48" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
-    <hyperlink ref="E62" r:id="rId49" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
-    <hyperlink ref="E63" r:id="rId50" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
-    <hyperlink ref="E64" r:id="rId51" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
-    <hyperlink ref="E65" r:id="rId52" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
-    <hyperlink ref="E66" r:id="rId53" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
-    <hyperlink ref="E67" r:id="rId54" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
-    <hyperlink ref="E23" r:id="rId55" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
-    <hyperlink ref="E68" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
-    <hyperlink ref="E69" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
+    <hyperlink ref="E13" r:id="rId11" xr:uid="{8EA6AEE0-BF75-4882-8D24-5523F8FC3EF2}"/>
+    <hyperlink ref="E57" r:id="rId12" xr:uid="{AEF2F350-0DDD-4CC3-83D9-532309D4CF1A}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{87A071E2-C82E-43C2-AFF8-07FB59401B4F}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{B46330A8-2538-449E-9B35-322B39604CD0}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{AF04CD14-06B0-477F-854A-FBF0C5FC46C6}"/>
+    <hyperlink ref="E20" r:id="rId16" xr:uid="{456736E6-F5EC-4F85-8E29-563F7384B7FC}"/>
+    <hyperlink ref="E21" r:id="rId17" xr:uid="{E7D78594-C200-4A80-AF9E-B4E73D1A0F07}"/>
+    <hyperlink ref="E22" r:id="rId18" xr:uid="{E91A31D9-E26E-45C1-BED2-8643687FEA6C}"/>
+    <hyperlink ref="E23" r:id="rId19" xr:uid="{13486532-E25E-4444-9FD0-D2523BB3A586}"/>
+    <hyperlink ref="E26" r:id="rId20" xr:uid="{40D2A6AA-BCA3-4EDD-87F7-0E98FD6FA310}"/>
+    <hyperlink ref="E29" r:id="rId21" xr:uid="{979A5FE7-1E83-44AA-8575-B6687D6D0E90}"/>
+    <hyperlink ref="E31" r:id="rId22" xr:uid="{DF38906D-90C8-4794-BCBF-61442F1F47A9}"/>
+    <hyperlink ref="E32" r:id="rId23" xr:uid="{148BE5EB-22A7-4640-A43A-4BBBA78B8020}"/>
+    <hyperlink ref="E33" r:id="rId24" xr:uid="{C67A4692-07D1-4E77-9FDE-08AB7A9F123C}"/>
+    <hyperlink ref="E36" r:id="rId25" xr:uid="{BF64A6D5-AF37-4B6A-8B44-FFA31C249E90}"/>
+    <hyperlink ref="E37" r:id="rId26" xr:uid="{A14B6C9C-465E-48BB-9D5C-4296BB57B151}"/>
+    <hyperlink ref="E38" r:id="rId27" xr:uid="{39510443-E7E4-4CE9-8E4A-D08B3E9C85DD}"/>
+    <hyperlink ref="E39" r:id="rId28" xr:uid="{3B5C8AA2-9997-4D42-9810-45FB1BA410F5}"/>
+    <hyperlink ref="E40" r:id="rId29" xr:uid="{49C1B852-AC98-4776-B42F-9E128C26964E}"/>
+    <hyperlink ref="E41" r:id="rId30" xr:uid="{E0221E73-A5B2-4224-B1C3-069D79890AA1}"/>
+    <hyperlink ref="E42" r:id="rId31" xr:uid="{715A4C08-CD9A-4986-9020-4D01FCC2E174}"/>
+    <hyperlink ref="E44" r:id="rId32" xr:uid="{81F685FB-18AB-40F4-A239-37FEC5A4CC1B}"/>
+    <hyperlink ref="E46" r:id="rId33" xr:uid="{13E1EA31-291A-45AD-A6CE-5082E549CC91}"/>
+    <hyperlink ref="E47" r:id="rId34" xr:uid="{463B1EF7-F3D4-4401-8BA1-AE1106774857}"/>
+    <hyperlink ref="E48" r:id="rId35" xr:uid="{4C64A978-F73B-4864-B8CE-76430ACCE933}"/>
+    <hyperlink ref="E49" r:id="rId36" xr:uid="{77837C35-769C-4BAD-AF95-5DB752134854}"/>
+    <hyperlink ref="E50" r:id="rId37" xr:uid="{6FEB8DAF-42EC-44F5-ACB7-346110109C62}"/>
+    <hyperlink ref="E51" r:id="rId38" xr:uid="{69ACB0D9-BED9-482F-BC8D-D6C2B535CDCA}"/>
+    <hyperlink ref="E52" r:id="rId39" xr:uid="{5F845DF1-FFB0-4A1A-8DD6-6696EBB8C869}"/>
+    <hyperlink ref="E53" r:id="rId40" xr:uid="{B391D205-86ED-47E3-8E9D-036DBEE2748E}"/>
+    <hyperlink ref="E54" r:id="rId41" xr:uid="{E362429D-20F8-4EAA-9815-6EAE94B7B465}"/>
+    <hyperlink ref="E55" r:id="rId42" xr:uid="{3D5EBA38-EE1C-4355-A27B-5536D7ADAC2C}"/>
+    <hyperlink ref="E56" r:id="rId43" xr:uid="{E047D85B-2879-4DD2-9D6D-9007A4573524}"/>
+    <hyperlink ref="E58" r:id="rId44" xr:uid="{51CB0607-1758-44AC-AA97-411B37EA4DF2}"/>
+    <hyperlink ref="E59" r:id="rId45" xr:uid="{3DDA757E-5369-45FE-8361-14E61E25F58B}"/>
+    <hyperlink ref="E60" r:id="rId46" xr:uid="{B6E6FF11-5547-42AA-998A-D83611AB225A}"/>
+    <hyperlink ref="E61" r:id="rId47" xr:uid="{8883127D-7E95-4EC9-B49B-1273AD9B34FE}"/>
+    <hyperlink ref="E62" r:id="rId48" xr:uid="{29D7E259-4058-458C-AE9D-B3FE0FC387DE}"/>
+    <hyperlink ref="E63" r:id="rId49" xr:uid="{226A6085-DC40-48CD-AC61-83C7367D6094}"/>
+    <hyperlink ref="E64" r:id="rId50" display="mailto:escolaindigena_temanare@seduc.to.gov.br" xr:uid="{128FE3F8-2C6C-4DE3-8EE7-DD1A9DA92BC1}"/>
+    <hyperlink ref="E65" r:id="rId51" xr:uid="{4902D51B-5926-44A8-A601-1FE11B4493EF}"/>
+    <hyperlink ref="E66" r:id="rId52" xr:uid="{139FDA3C-B039-42B5-990E-157F8B1ED884}"/>
+    <hyperlink ref="E67" r:id="rId53" xr:uid="{0720110E-7BFA-40FF-A506-42192E1DCB28}"/>
+    <hyperlink ref="E68" r:id="rId54" xr:uid="{D995FEB4-8569-4AA0-A971-E2B2B6A5740E}"/>
+    <hyperlink ref="E24" r:id="rId55" xr:uid="{EFD0FE3D-FFAD-4DF5-A48F-C2E4F3460C4E}"/>
+    <hyperlink ref="E69" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
+    <hyperlink ref="E70" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
+    <hyperlink ref="E7" r:id="rId58" xr:uid="{837AFF8C-CBEC-495D-8C54-2EF7EE097514}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId58"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
 </worksheet>
 </file>
--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\OneDrive\Área de Trabalho\Projeto Python\Painel SGE\Painel 1 - Copia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D96021-6FF2-42BC-831F-A67A5FC3C5D3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
   <si>
     <t>CPF</t>
   </si>
@@ -482,6 +482,12 @@
   </si>
   <si>
     <t>alline.lira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>andrea.pina@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ANDRÉA MARTINS DE PINA</t>
   </si>
 </sst>
 </file>
@@ -856,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
@@ -1818,6 +1824,14 @@
       </c>
       <c r="E70" s="2" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/login_senha.xlsx
+++ b/login_senha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bf22f0b01d7fe6/Área de Trabalho/Projeto Python/Painel SGE/Painel 1 - Copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D96021-6FF2-42BC-831F-A67A5FC3C5D3}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{A2AAB9F9-1CC5-4B01-8202-B5B8986FFE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F42F1A55-F2DB-470F-B520-4CDEFC56C48C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="236">
   <si>
     <t>CPF</t>
   </si>
@@ -489,12 +489,267 @@
   <si>
     <t>ANDRÉA MARTINS DE PINA</t>
   </si>
+  <si>
+    <t>KEILA DUARTE LIMA ROSA</t>
+  </si>
+  <si>
+    <t>ZILMA SALES DE SOUZA</t>
+  </si>
+  <si>
+    <t>LUSIVONE GONCALVES ABREU PINHEIRO</t>
+  </si>
+  <si>
+    <t>ELIANE ALVES DE AZEVEDO SANTANA</t>
+  </si>
+  <si>
+    <t>DEBORA REGINA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>LUCIANA PEREIRA GOMES</t>
+  </si>
+  <si>
+    <t>JULIANA FRASCARI PINTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MARIA IRANY BARBOSA PINTO</t>
+  </si>
+  <si>
+    <t>REIJANE ALVES DOS SANTOS MACEDO</t>
+  </si>
+  <si>
+    <t>ROSANGELA MENDES MACIEL SANTOS</t>
+  </si>
+  <si>
+    <t>LUDIMILLA RAMOS SILVA BEZERRA</t>
+  </si>
+  <si>
+    <t>SUENNY FERREIRA CRUZ</t>
+  </si>
+  <si>
+    <t>POLLYANA DE GODOY BORGES</t>
+  </si>
+  <si>
+    <t>SYNARA NUNES RIBEIRO</t>
+  </si>
+  <si>
+    <t>ELIUDE FERNANDES DA SILVA MOURA</t>
+  </si>
+  <si>
+    <t>MARIA JOANA MONTEIRO PORTILHO BARROS</t>
+  </si>
+  <si>
+    <t>POLIANA FERREIRA DE MOURA COÊLHO</t>
+  </si>
+  <si>
+    <t>LINA MARIA DA SILVA CONCESSO</t>
+  </si>
+  <si>
+    <t>AYRANA GOMES FERREIRA</t>
+  </si>
+  <si>
+    <t>ROSEANE SOUZA PEREIRA</t>
+  </si>
+  <si>
+    <t>LIDIANE RODRIGUES PEREIRA</t>
+  </si>
+  <si>
+    <t>ALINE REIS DOS SANTOS MARTINS</t>
+  </si>
+  <si>
+    <t>MARLI FERREIRA VIEIRA FONSECA</t>
+  </si>
+  <si>
+    <t>VIVIANO IESORU JAVAÉ KARAJÁ</t>
+  </si>
+  <si>
+    <t>CLAUDILENE SEIJA TORRES JAVAÉ</t>
+  </si>
+  <si>
+    <t>ORLENE DE SOUSA R. JÁCOME</t>
+  </si>
+  <si>
+    <t>VALDIRENE ALVES LIMA</t>
+  </si>
+  <si>
+    <t>MARIA DE FÁTIMA MARQUES DE OLIVEIRA SANTANA</t>
+  </si>
+  <si>
+    <t>626.250.041-34</t>
+  </si>
+  <si>
+    <t>623.532.171-68</t>
+  </si>
+  <si>
+    <t>575.111.281-49</t>
+  </si>
+  <si>
+    <t>758.444.861-53</t>
+  </si>
+  <si>
+    <t>371.383.751-15</t>
+  </si>
+  <si>
+    <t>008.869.971-43</t>
+  </si>
+  <si>
+    <t>038.389.916-80</t>
+  </si>
+  <si>
+    <t>003.073.171-29</t>
+  </si>
+  <si>
+    <t>012.087.871-28</t>
+  </si>
+  <si>
+    <t>827.967.001-78</t>
+  </si>
+  <si>
+    <t>000.010.751-44</t>
+  </si>
+  <si>
+    <t>003.885.911-45</t>
+  </si>
+  <si>
+    <t>014.827.731-47</t>
+  </si>
+  <si>
+    <t>882.447.251-68</t>
+  </si>
+  <si>
+    <t>985.670.631-91</t>
+  </si>
+  <si>
+    <t>800.627.251-49</t>
+  </si>
+  <si>
+    <t>019.762.211-96</t>
+  </si>
+  <si>
+    <t>340.951.601-87</t>
+  </si>
+  <si>
+    <t>076.079.991-16</t>
+  </si>
+  <si>
+    <t>034.963.001-16</t>
+  </si>
+  <si>
+    <t>010.515.591-89</t>
+  </si>
+  <si>
+    <t>066.914.441-08</t>
+  </si>
+  <si>
+    <t>435.003.151-00</t>
+  </si>
+  <si>
+    <t>016.528.091-39</t>
+  </si>
+  <si>
+    <t>071.338.531-67</t>
+  </si>
+  <si>
+    <t>451.680.081-00</t>
+  </si>
+  <si>
+    <t>006.309.481-94</t>
+  </si>
+  <si>
+    <t>315.567.871-20</t>
+  </si>
+  <si>
+    <t>964.858.761-20</t>
+  </si>
+  <si>
+    <t>lusivoneabreu01@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>elianeasantana@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>deboraazevedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>lucianapereiragomes@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>julianafrascarioliveira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariairanypinto17@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>reijanealvesmacedo@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>rosangelammaciel@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>Não Possui (E preciso solicitar)</t>
+  </si>
+  <si>
+    <t>suennycruz@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>pollyana.borges@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>synararibeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>eliudesilvamoura@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>mariajoanaportilhobarros@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>poliana.coelho@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lina.concesso@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>ayrana.ferreira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>roseanesouza@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>lidiane.pereira@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>marlifonseca@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t>vivianokaraja202323@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>claudilene.javae@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>orlene.jacome@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>valdirene.lima@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t>maria.fatimasantana@professor.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea.pina@professor.to.gov.br </t>
+  </si>
+  <si>
+    <t>zilmaribeiro@seduc.to.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keilarosa@seduc.to.gov.br </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -517,6 +772,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -526,7 +787,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -534,12 +795,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -547,6 +823,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -563,6 +842,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -862,13 +1145,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1830,7 +2113,370 @@
       <c r="A71" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1895,8 +2541,10 @@
     <hyperlink ref="E69" r:id="rId56" xr:uid="{4B244151-2680-40D9-98CA-1C6CAEEA6051}"/>
     <hyperlink ref="E70" r:id="rId57" xr:uid="{8712D512-6735-468E-84CA-60F3EEE40E85}"/>
     <hyperlink ref="E7" r:id="rId58" xr:uid="{837AFF8C-CBEC-495D-8C54-2EF7EE097514}"/>
+    <hyperlink ref="E71" r:id="rId59" xr:uid="{8578D14F-F5C7-4B4F-9324-52C4E9DDA4D9}"/>
+    <hyperlink ref="E72" r:id="rId60" xr:uid="{03D3228E-2A04-4F16-B558-0099E265701C}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId61"/>
 </worksheet>
 </file>